--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc7a8982f01e4d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd9cf02c93a9e426e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd9cf02c93a9e426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2d243367fb454f85"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2d243367fb454f85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R138097efff424fc2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R138097efff424fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re07cb109732246d6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re07cb109732246d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc8330eafb1c348f5"/>
   </x:sheets>
 </x:workbook>
 </file>
